--- a/reports/Summary.xlsx
+++ b/reports/Summary.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EXE_20260704_144216_01e9c4ca</t>
+          <t>EXE_20260704_080604_ac137122</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04T14:42:16.161700</t>
+          <t>2026-07-04T08:06:04.179569</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1 (100.0%)</t>
+          <t>0 (0.0%)</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>16 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5.84s</t>
+          <t>14.65s</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5.84s</t>
+          <t>0.92s</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>3.14.6 (v3.14.6:c63aec69bd5, Jun 10 2026, 08:07:54) [Clang 21.0.0 (clang-2100.1.1.101)]</t>
+          <t>3.12.3 (main, Mar 23 2026, 19:04:32) [GCC 13.3.0]</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>macOS-26.5.1-arm64-arm-64bit-Mach-O</t>
+          <t>Linux-6.17.0-1018-azure-x86_64-with-glibc2.39</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Muhammads-MacBook-Air-2.local</t>
+          <t>runnervmmklqx</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Darwin 25.5.0</t>
+          <t>Linux 6.17.0-1018-azure</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>arm</t>
+          <t>x86_64</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>arm64</t>
+          <t>x86_64</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -816,17 +816,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>3.21s</t>
+          <t>0.00s</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.00s</t>
+          <t>0.05s</t>
         </is>
       </c>
     </row>
@@ -904,27 +904,135 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>Smoke</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Test_open.py</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
